--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/60.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/60.xlsx
@@ -426,13 +426,13 @@
         <v>-6.642449588155677</v>
       </c>
       <c r="E2">
-        <v>-18.58420296187485</v>
+        <v>-14.3246029757495</v>
       </c>
       <c r="F2">
-        <v>-2.100109493153524</v>
+        <v>-1.430392672072985</v>
       </c>
       <c r="G2">
-        <v>-4.507832466470603</v>
+        <v>-2.210870657018632</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.690491866645888</v>
       </c>
       <c r="E3">
-        <v>-18.52575066568922</v>
+        <v>-15.57632272409428</v>
       </c>
       <c r="F3">
-        <v>-1.501112882352187</v>
+        <v>-1.586303014423491</v>
       </c>
       <c r="G3">
-        <v>-4.670539290877966</v>
+        <v>-1.417465375779305</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.857326342349473</v>
       </c>
       <c r="E4">
-        <v>-18.79464617970392</v>
+        <v>-14.9534240895965</v>
       </c>
       <c r="F4">
-        <v>-1.953185280388587</v>
+        <v>-1.82919027733314</v>
       </c>
       <c r="G4">
-        <v>-3.737396516143891</v>
+        <v>-0.7276727151274903</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.264408596354074</v>
       </c>
       <c r="E5">
-        <v>-18.17818502275962</v>
+        <v>-16.30073830300485</v>
       </c>
       <c r="F5">
-        <v>-2.226129026141412</v>
+        <v>-1.671341555260083</v>
       </c>
       <c r="G5">
-        <v>-2.547074513228428</v>
+        <v>-0.1977698854692267</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.884908702347782</v>
       </c>
       <c r="E6">
-        <v>-18.6581135106115</v>
+        <v>-16.03166004769186</v>
       </c>
       <c r="F6">
-        <v>-2.171973678815992</v>
+        <v>-1.889735650803755</v>
       </c>
       <c r="G6">
-        <v>-2.176400996182164</v>
+        <v>0.4062833120658365</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.721580592907282</v>
       </c>
       <c r="E7">
-        <v>-19.68845463570894</v>
+        <v>-16.91719945994915</v>
       </c>
       <c r="F7">
-        <v>-2.542921571994027</v>
+        <v>-2.097759414831781</v>
       </c>
       <c r="G7">
-        <v>-1.443001068624984</v>
+        <v>1.164657622381606</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.731306686936335</v>
       </c>
       <c r="E8">
-        <v>-20.41515448084817</v>
+        <v>-17.23137328382713</v>
       </c>
       <c r="F8">
-        <v>-2.785512279373474</v>
+        <v>-2.21301431342029</v>
       </c>
       <c r="G8">
-        <v>-0.8951441484136342</v>
+        <v>2.043982508114472</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.885853207379891</v>
       </c>
       <c r="E9">
-        <v>-20.13136970423396</v>
+        <v>-17.42445607831841</v>
       </c>
       <c r="F9">
-        <v>-2.559347269224139</v>
+        <v>-2.249410291997092</v>
       </c>
       <c r="G9">
-        <v>-1.414118401213498</v>
+        <v>2.040382291323326</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.125559801714283</v>
       </c>
       <c r="E10">
-        <v>-20.7013854989327</v>
+        <v>-17.59017751660172</v>
       </c>
       <c r="F10">
-        <v>-2.619910038410213</v>
+        <v>-1.979545587880472</v>
       </c>
       <c r="G10">
-        <v>-0.5596895759014882</v>
+        <v>2.411431755590711</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.406252086152835</v>
       </c>
       <c r="E11">
-        <v>-19.71377676515642</v>
+        <v>-17.85886121683885</v>
       </c>
       <c r="F11">
-        <v>-2.465137872871153</v>
+        <v>-1.643488529708352</v>
       </c>
       <c r="G11">
-        <v>-0.09390402265637574</v>
+        <v>2.836319994816034</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.678444033807081</v>
       </c>
       <c r="E12">
-        <v>-21.92542409379749</v>
+        <v>-18.18434838836566</v>
       </c>
       <c r="F12">
-        <v>-1.869997312329849</v>
+        <v>-1.258546197627422</v>
       </c>
       <c r="G12">
-        <v>-0.6841019986464006</v>
+        <v>2.9208506831871</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.903816269910605</v>
       </c>
       <c r="E13">
-        <v>-20.80366663422925</v>
+        <v>-19.20548184395595</v>
       </c>
       <c r="F13">
-        <v>-2.480333444508108</v>
+        <v>-1.202729145291985</v>
       </c>
       <c r="G13">
-        <v>-0.05495432410155663</v>
+        <v>3.01345901532307</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.067531741048546</v>
       </c>
       <c r="E14">
-        <v>-22.65938790554384</v>
+        <v>-19.79675377421517</v>
       </c>
       <c r="F14">
-        <v>-2.424845254031583</v>
+        <v>-0.923094676026748</v>
       </c>
       <c r="G14">
-        <v>-1.427736045000745</v>
+        <v>3.383391080905458</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.159714010251355</v>
       </c>
       <c r="E15">
-        <v>-23.98514695217634</v>
+        <v>-20.00493764508353</v>
       </c>
       <c r="F15">
-        <v>-1.253715158934295</v>
+        <v>-1.158348533319599</v>
       </c>
       <c r="G15">
-        <v>-0.1353991971875303</v>
+        <v>2.984312662707882</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.195828826740912</v>
       </c>
       <c r="E16">
-        <v>-22.89082560661991</v>
+        <v>-20.46847756104764</v>
       </c>
       <c r="F16">
-        <v>-1.179352617184984</v>
+        <v>-0.3433998540780428</v>
       </c>
       <c r="G16">
-        <v>-0.1017519208972623</v>
+        <v>3.114082333353759</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.189339017007558</v>
       </c>
       <c r="E17">
-        <v>-24.14338015044098</v>
+        <v>-21.67501452338961</v>
       </c>
       <c r="F17">
-        <v>-1.258197454950843</v>
+        <v>-0.2274391864623484</v>
       </c>
       <c r="G17">
-        <v>0.1274636219687109</v>
+        <v>2.945913831261787</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.16406517963653</v>
       </c>
       <c r="E18">
-        <v>-25.12065984765241</v>
+        <v>-21.10873246567188</v>
       </c>
       <c r="F18">
-        <v>-0.9782515195421531</v>
+        <v>0.1650504010254882</v>
       </c>
       <c r="G18">
-        <v>0.3521416907353291</v>
+        <v>2.521440700426452</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.141190967731432</v>
       </c>
       <c r="E19">
-        <v>-25.07147336593246</v>
+        <v>-22.38641809121949</v>
       </c>
       <c r="F19">
-        <v>-0.3583858487620887</v>
+        <v>0.4868272335407477</v>
       </c>
       <c r="G19">
-        <v>1.01932008173892</v>
+        <v>2.293225072738875</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.13209051803379</v>
       </c>
       <c r="E20">
-        <v>-25.7808127877339</v>
+        <v>-23.53198591131297</v>
       </c>
       <c r="F20">
-        <v>0.06985773256538015</v>
+        <v>1.146958187036091</v>
       </c>
       <c r="G20">
-        <v>-0.4926404333125168</v>
+        <v>2.422811991263374</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.150467198289491</v>
       </c>
       <c r="E21">
-        <v>-26.50851771001374</v>
+        <v>-24.16846139363162</v>
       </c>
       <c r="F21">
-        <v>-0.5653476457797255</v>
+        <v>1.25458796368183</v>
       </c>
       <c r="G21">
-        <v>1.625430546011781</v>
+        <v>2.268501321461032</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.192008990230054</v>
       </c>
       <c r="E22">
-        <v>-27.88058090970674</v>
+        <v>-24.05192228385693</v>
       </c>
       <c r="F22">
-        <v>0.4203466076290734</v>
+        <v>1.669899901484196</v>
       </c>
       <c r="G22">
-        <v>0.6578363856533749</v>
+        <v>1.49032973491085</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.25471051825602</v>
       </c>
       <c r="E23">
-        <v>-27.18536655962104</v>
+        <v>-24.52144697734012</v>
       </c>
       <c r="F23">
-        <v>0.4186492828207372</v>
+        <v>1.671695802013465</v>
       </c>
       <c r="G23">
-        <v>-0.03157249554354604</v>
+        <v>1.36725923488577</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.326084331604395</v>
       </c>
       <c r="E24">
-        <v>-28.21091072563831</v>
+        <v>-25.26601393759876</v>
       </c>
       <c r="F24">
-        <v>0.6346560235095419</v>
+        <v>1.860149386150353</v>
       </c>
       <c r="G24">
-        <v>-1.400046487867397</v>
+        <v>1.526243137506205</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.388231884177981</v>
       </c>
       <c r="E25">
-        <v>-27.33684248306019</v>
+        <v>-25.9233136215001</v>
       </c>
       <c r="F25">
-        <v>1.352270704554754</v>
+        <v>2.099410056570545</v>
       </c>
       <c r="G25">
-        <v>-0.3641500275162853</v>
+        <v>1.199202994811217</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.43183709756291</v>
       </c>
       <c r="E26">
-        <v>-27.38306772510553</v>
+        <v>-25.83533199279493</v>
       </c>
       <c r="F26">
-        <v>0.7622859027284729</v>
+        <v>2.513356844893098</v>
       </c>
       <c r="G26">
-        <v>-1.211947561566867</v>
+        <v>0.7035218052532662</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.439797417632347</v>
       </c>
       <c r="E27">
-        <v>-28.1989660898681</v>
+        <v>-26.97897687604501</v>
       </c>
       <c r="F27">
-        <v>-0.01223844725646765</v>
+        <v>2.5791060223881</v>
       </c>
       <c r="G27">
-        <v>-0.10573330639871</v>
+        <v>1.147698225517734</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.409911452373499</v>
       </c>
       <c r="E28">
-        <v>-28.10052044523003</v>
+        <v>-25.99786376478077</v>
       </c>
       <c r="F28">
-        <v>1.784390216959921</v>
+        <v>3.021754084482849</v>
       </c>
       <c r="G28">
-        <v>-0.1513116854703658</v>
+        <v>0.7487216263592106</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.337021272432251</v>
       </c>
       <c r="E29">
-        <v>-27.59093179870188</v>
+        <v>-25.82181744314394</v>
       </c>
       <c r="F29">
-        <v>1.117131990330892</v>
+        <v>2.645252816236446</v>
       </c>
       <c r="G29">
-        <v>-0.8177799539451742</v>
+        <v>0.632903774808243</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.223371511318397</v>
       </c>
       <c r="E30">
-        <v>-28.17281747136698</v>
+        <v>-26.1164670205839</v>
       </c>
       <c r="F30">
-        <v>1.075622499776608</v>
+        <v>2.924926218769615</v>
       </c>
       <c r="G30">
-        <v>-0.6345004621598394</v>
+        <v>0.9143185450289352</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.07693052187649</v>
       </c>
       <c r="E31">
-        <v>-28.88663613158225</v>
+        <v>-25.47215027528397</v>
       </c>
       <c r="F31">
-        <v>1.240719436624161</v>
+        <v>2.695630808205101</v>
       </c>
       <c r="G31">
-        <v>0.04941541241737919</v>
+        <v>1.222665756451552</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.900132945429946</v>
       </c>
       <c r="E32">
-        <v>-27.30308102820066</v>
+        <v>-25.27941219733265</v>
       </c>
       <c r="F32">
-        <v>0.609869614082975</v>
+        <v>2.602152860268788</v>
       </c>
       <c r="G32">
-        <v>-0.7065857310650683</v>
+        <v>1.750921206272823</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.704537505052103</v>
       </c>
       <c r="E33">
-        <v>-26.54100828220787</v>
+        <v>-25.04770038430915</v>
       </c>
       <c r="F33">
-        <v>0.9744755264251774</v>
+        <v>2.17510792657317</v>
       </c>
       <c r="G33">
-        <v>-0.6819011409560922</v>
+        <v>1.323576256387263</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.492677387162152</v>
       </c>
       <c r="E34">
-        <v>-27.06550903399782</v>
+        <v>-24.86048192420852</v>
       </c>
       <c r="F34">
-        <v>0.1406591228500567</v>
+        <v>2.360380579883307</v>
       </c>
       <c r="G34">
-        <v>-0.1511237118598056</v>
+        <v>1.505127435253281</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.270152514631496</v>
       </c>
       <c r="E35">
-        <v>-27.09991838982402</v>
+        <v>-24.73645872762649</v>
       </c>
       <c r="F35">
-        <v>0.6298630897169439</v>
+        <v>1.700983559906845</v>
       </c>
       <c r="G35">
-        <v>-0.6785515556456938</v>
+        <v>1.963015486110275</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.040384810997811</v>
       </c>
       <c r="E36">
-        <v>-26.52455741215023</v>
+        <v>-24.22989154233716</v>
       </c>
       <c r="F36">
-        <v>0.633048162380708</v>
+        <v>2.192240221197869</v>
       </c>
       <c r="G36">
-        <v>0.2749054227518337</v>
+        <v>2.274633960505557</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.799415326324291</v>
       </c>
       <c r="E37">
-        <v>-24.89738320682963</v>
+        <v>-23.52742568527831</v>
       </c>
       <c r="F37">
-        <v>-0.3827928659181733</v>
+        <v>1.639097887978499</v>
       </c>
       <c r="G37">
-        <v>0.9106896100472877</v>
+        <v>2.45980885286404</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.549811093868944</v>
       </c>
       <c r="E38">
-        <v>-26.58516937822477</v>
+        <v>-22.93619944034366</v>
       </c>
       <c r="F38">
-        <v>0.198116342643036</v>
+        <v>1.59605094752462</v>
       </c>
       <c r="G38">
-        <v>0.9538086677141148</v>
+        <v>2.941110061214139</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.285034853899288</v>
       </c>
       <c r="E39">
-        <v>-26.14295620241365</v>
+        <v>-22.70374420249301</v>
       </c>
       <c r="F39">
-        <v>0.7628707301148494</v>
+        <v>1.377101845821072</v>
       </c>
       <c r="G39">
-        <v>0.5931708528760898</v>
+        <v>3.270867989028476</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.004391064682973</v>
       </c>
       <c r="E40">
-        <v>-24.916733018392</v>
+        <v>-22.64459001359348</v>
       </c>
       <c r="F40">
-        <v>-0.06649899724204367</v>
+        <v>0.9733390063485365</v>
       </c>
       <c r="G40">
-        <v>0.7023548024210386</v>
+        <v>3.551053098546753</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.706548964854889</v>
       </c>
       <c r="E41">
-        <v>-24.95714376458258</v>
+        <v>-22.66126515706267</v>
       </c>
       <c r="F41">
-        <v>0.3019082931116057</v>
+        <v>1.140109245349744</v>
       </c>
       <c r="G41">
-        <v>2.158761283318176</v>
+        <v>3.644925031064823</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.390224290330647</v>
       </c>
       <c r="E42">
-        <v>-23.42886998054012</v>
+        <v>-22.24280004360692</v>
       </c>
       <c r="F42">
-        <v>-0.323542230698133</v>
+        <v>0.8337657259160423</v>
       </c>
       <c r="G42">
-        <v>2.188461113786681</v>
+        <v>4.05286953789382</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.06211698315685</v>
       </c>
       <c r="E43">
-        <v>-22.42559118043527</v>
+        <v>-20.54595571831232</v>
       </c>
       <c r="F43">
-        <v>-0.8562851882561623</v>
+        <v>0.4741167641121921</v>
       </c>
       <c r="G43">
-        <v>1.056092419304751</v>
+        <v>4.706130049482187</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.724548731245776</v>
       </c>
       <c r="E44">
-        <v>-25.48150330718748</v>
+        <v>-20.6685668230439</v>
       </c>
       <c r="F44">
-        <v>0.1698358795114609</v>
+        <v>0.5428811989533846</v>
       </c>
       <c r="G44">
-        <v>2.118519266190756</v>
+        <v>4.512350142951394</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.388824823511482</v>
       </c>
       <c r="E45">
-        <v>-22.0306249366554</v>
+        <v>-20.71223368691315</v>
       </c>
       <c r="F45">
-        <v>-0.6675309067520585</v>
+        <v>0.2623645184041656</v>
       </c>
       <c r="G45">
-        <v>1.430102467938458</v>
+        <v>4.525876410677952</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.064051358624986</v>
       </c>
       <c r="E46">
-        <v>-22.39760684252857</v>
+        <v>-19.96484254295363</v>
       </c>
       <c r="F46">
-        <v>-0.2278401162853034</v>
+        <v>0.3684651288243375</v>
       </c>
       <c r="G46">
-        <v>1.456745116490769</v>
+        <v>4.27475933143713</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.761728229401948</v>
       </c>
       <c r="E47">
-        <v>-20.4276390340906</v>
+        <v>-19.87519132329588</v>
       </c>
       <c r="F47">
-        <v>-0.6297325021623171</v>
+        <v>-0.01363921653460161</v>
       </c>
       <c r="G47">
-        <v>2.25576349860099</v>
+        <v>4.422417824021315</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4943432431921045</v>
       </c>
       <c r="E48">
-        <v>-21.33063439354615</v>
+        <v>-19.46621629771737</v>
       </c>
       <c r="F48">
-        <v>0.08032332633234911</v>
+        <v>0.01219756275871497</v>
       </c>
       <c r="G48">
-        <v>1.108255096235194</v>
+        <v>3.997318114484112</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2683778833696369</v>
       </c>
       <c r="E49">
-        <v>-21.36755228901255</v>
+        <v>-18.9323791268692</v>
       </c>
       <c r="F49">
-        <v>-0.219756078801383</v>
+        <v>-0.1124129172770119</v>
       </c>
       <c r="G49">
-        <v>1.243577820626369</v>
+        <v>4.235867069263315</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.09392515291235493</v>
       </c>
       <c r="E50">
-        <v>-20.81333946340478</v>
+        <v>-18.9494903575275</v>
       </c>
       <c r="F50">
-        <v>-0.7414668392889284</v>
+        <v>-0.0146721906858926</v>
       </c>
       <c r="G50">
-        <v>0.01947017195730981</v>
+        <v>4.481402376568338</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.02690860323741846</v>
       </c>
       <c r="E51">
-        <v>-20.14319389687574</v>
+        <v>-17.86561849166435</v>
       </c>
       <c r="F51">
-        <v>-0.1154223760513825</v>
+        <v>-0.1797500750831809</v>
       </c>
       <c r="G51">
-        <v>1.046372617192036</v>
+        <v>4.563604280764131</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.09027417015748576</v>
       </c>
       <c r="E52">
-        <v>-19.70312377810824</v>
+        <v>-17.36455846459173</v>
       </c>
       <c r="F52">
-        <v>-0.4616145093967546</v>
+        <v>-0.2824046771077068</v>
       </c>
       <c r="G52">
-        <v>0.8392622487790193</v>
+        <v>4.261525467104777</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.09768089023408279</v>
       </c>
       <c r="E53">
-        <v>-19.59974619502193</v>
+        <v>-18.42189131008923</v>
       </c>
       <c r="F53">
-        <v>-0.3363951793199702</v>
+        <v>-0.6282008508345408</v>
       </c>
       <c r="G53">
-        <v>0.3705657153148156</v>
+        <v>4.183461593085898</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.05259903803211487</v>
       </c>
       <c r="E54">
-        <v>-19.01587113413223</v>
+        <v>-17.15854257003494</v>
       </c>
       <c r="F54">
-        <v>-0.1189288552674328</v>
+        <v>-0.3199719671920672</v>
       </c>
       <c r="G54">
-        <v>0.1535893430919815</v>
+        <v>4.312962357038891</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.04075409204933573</v>
       </c>
       <c r="E55">
-        <v>-17.60695649035402</v>
+        <v>-17.72333777809837</v>
       </c>
       <c r="F55">
-        <v>-0.4549130171081067</v>
+        <v>-0.4993408460224525</v>
       </c>
       <c r="G55">
-        <v>-0.8580689644752345</v>
+        <v>4.128578520291515</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.1736402054985575</v>
       </c>
       <c r="E56">
-        <v>-19.10880754394792</v>
+        <v>-16.9184620361919</v>
       </c>
       <c r="F56">
-        <v>0.02842776528176568</v>
+        <v>-0.5729967903771762</v>
       </c>
       <c r="G56">
-        <v>-0.1580656817275758</v>
+        <v>3.634338461747859</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.3406418846048411</v>
       </c>
       <c r="E57">
-        <v>-19.75570758669189</v>
+        <v>-16.91621514886516</v>
       </c>
       <c r="F57">
-        <v>-0.8014696321107107</v>
+        <v>-0.6819213052734916</v>
       </c>
       <c r="G57">
-        <v>-0.1800951445873898</v>
+        <v>3.520930327454489</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.5319381279037239</v>
       </c>
       <c r="E58">
-        <v>-18.51086555630103</v>
+        <v>-16.6482291881306</v>
       </c>
       <c r="F58">
-        <v>-0.8795092967610493</v>
+        <v>-0.7390620887186015</v>
       </c>
       <c r="G58">
-        <v>0.8286182430810505</v>
+        <v>3.411378262922193</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.7433458336165999</v>
       </c>
       <c r="E59">
-        <v>-16.36077297270525</v>
+        <v>-17.76221183609876</v>
       </c>
       <c r="F59">
-        <v>-1.36081975064666</v>
+        <v>-0.8492274979843105</v>
       </c>
       <c r="G59">
-        <v>-0.2641219592523709</v>
+        <v>3.749138122908292</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.9690255182378468</v>
       </c>
       <c r="E60">
-        <v>-19.94869070411137</v>
+        <v>-16.46260556117872</v>
       </c>
       <c r="F60">
-        <v>-2.166192502711854</v>
+        <v>-0.9048117790795601</v>
       </c>
       <c r="G60">
-        <v>-0.4906484351894973</v>
+        <v>3.14705603753952</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.205775830494153</v>
       </c>
       <c r="E61">
-        <v>-16.82190817931228</v>
+        <v>-17.07660801701872</v>
       </c>
       <c r="F61">
-        <v>-1.288567889039681</v>
+        <v>-0.8311715737054897</v>
       </c>
       <c r="G61">
-        <v>-0.7219160233040856</v>
+        <v>2.632295526509713</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.453429910798356</v>
       </c>
       <c r="E62">
-        <v>-19.65238399535281</v>
+        <v>-16.79759528021674</v>
       </c>
       <c r="F62">
-        <v>-0.7456269003857875</v>
+        <v>-0.934366271276641</v>
       </c>
       <c r="G62">
-        <v>-0.6208201605024057</v>
+        <v>3.170983511717073</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.709193662591806</v>
       </c>
       <c r="E63">
-        <v>-17.49834586099843</v>
+        <v>-16.24500220702565</v>
       </c>
       <c r="F63">
-        <v>-0.7290719778408394</v>
+        <v>-1.250610437908602</v>
       </c>
       <c r="G63">
-        <v>-0.4853903955829952</v>
+        <v>3.157817526744088</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.975814656385714</v>
       </c>
       <c r="E64">
-        <v>-17.49658905260803</v>
+        <v>-16.04562729737725</v>
       </c>
       <c r="F64">
-        <v>-1.440351304989441</v>
+        <v>-1.19571784359469</v>
       </c>
       <c r="G64">
-        <v>-0.7760994165480506</v>
+        <v>2.955012276161817</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.24957972531806</v>
       </c>
       <c r="E65">
-        <v>-17.94586268767136</v>
+        <v>-15.51262492200538</v>
       </c>
       <c r="F65">
-        <v>-1.346169244760748</v>
+        <v>-1.362584173214623</v>
       </c>
       <c r="G65">
-        <v>-1.526693707982302</v>
+        <v>2.577574319879978</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.530494372528774</v>
       </c>
       <c r="E66">
-        <v>-15.73054807343046</v>
+        <v>-16.91286766053735</v>
       </c>
       <c r="F66">
-        <v>-1.361562796206971</v>
+        <v>-1.221356643078738</v>
       </c>
       <c r="G66">
-        <v>-0.532999933946537</v>
+        <v>2.169567155180794</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.815091948827448</v>
       </c>
       <c r="E67">
-        <v>-17.23803918800348</v>
+        <v>-16.42145554337231</v>
       </c>
       <c r="F67">
-        <v>-1.654967216808945</v>
+        <v>-1.369322113668994</v>
       </c>
       <c r="G67">
-        <v>-1.234512227067859</v>
+        <v>2.386551359637402</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.096641745628828</v>
       </c>
       <c r="E68">
-        <v>-17.83719806656854</v>
+        <v>-16.41621834389171</v>
       </c>
       <c r="F68">
-        <v>-1.42421884981992</v>
+        <v>-1.510747623614148</v>
       </c>
       <c r="G68">
-        <v>-2.145236537998044</v>
+        <v>1.670528548078672</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.371924511229655</v>
       </c>
       <c r="E69">
-        <v>-16.34277710803476</v>
+        <v>-15.65386733274015</v>
       </c>
       <c r="F69">
-        <v>-1.218367065122035</v>
+        <v>-1.813246689931458</v>
       </c>
       <c r="G69">
-        <v>-1.733999882239653</v>
+        <v>2.094662282117163</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.629870767210511</v>
       </c>
       <c r="E70">
-        <v>-16.77498519776437</v>
+        <v>-15.31469948310935</v>
       </c>
       <c r="F70">
-        <v>-1.175287818339446</v>
+        <v>-1.667722418077252</v>
       </c>
       <c r="G70">
-        <v>-2.464930045413639</v>
+        <v>1.524992590847062</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.866511631758152</v>
       </c>
       <c r="E71">
-        <v>-17.45097433262744</v>
+        <v>-15.87024133634107</v>
       </c>
       <c r="F71">
-        <v>-2.079194872967641</v>
+        <v>-1.86497906260369</v>
       </c>
       <c r="G71">
-        <v>-0.8458559012780065</v>
+        <v>1.862710678919703</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.074153392149284</v>
       </c>
       <c r="E72">
-        <v>-16.66943548515518</v>
+        <v>-15.59700571649193</v>
       </c>
       <c r="F72">
-        <v>-2.335998708244322</v>
+        <v>-1.648889485174605</v>
       </c>
       <c r="G72">
-        <v>-1.333018231235155</v>
+        <v>2.226564931093979</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.246561064405761</v>
       </c>
       <c r="E73">
-        <v>-17.72464603966569</v>
+        <v>-16.2442920078891</v>
       </c>
       <c r="F73">
-        <v>-1.77872199331758</v>
+        <v>-1.940682731178134</v>
       </c>
       <c r="G73">
-        <v>-1.161413989261278</v>
+        <v>1.259438094017383</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.382953403939122</v>
       </c>
       <c r="E74">
-        <v>-17.97478149812614</v>
+        <v>-16.12890333765139</v>
       </c>
       <c r="F74">
-        <v>-1.981196524114252</v>
+        <v>-2.13044099397443</v>
       </c>
       <c r="G74">
-        <v>-1.876063549165082</v>
+        <v>1.518309084693812</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.478408013891602</v>
       </c>
       <c r="E75">
-        <v>-17.05761538163028</v>
+        <v>-16.2184133481241</v>
       </c>
       <c r="F75">
-        <v>-2.023367051855969</v>
+        <v>-2.036211716803778</v>
       </c>
       <c r="G75">
-        <v>-1.027963168741931</v>
+        <v>1.587034325310278</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.537242810519239</v>
       </c>
       <c r="E76">
-        <v>-18.40774131910554</v>
+        <v>-16.11002283896872</v>
       </c>
       <c r="F76">
-        <v>-1.983457967123894</v>
+        <v>-1.919576758122205</v>
       </c>
       <c r="G76">
-        <v>-0.9825936492375649</v>
+        <v>1.839900603427146</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.559944923415085</v>
       </c>
       <c r="E77">
-        <v>-17.53366061689345</v>
+        <v>-16.85902542892228</v>
       </c>
       <c r="F77">
-        <v>-2.167472330349179</v>
+        <v>-2.079715916064003</v>
       </c>
       <c r="G77">
-        <v>-2.274217763777405</v>
+        <v>2.373792650820631</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.550719263650734</v>
       </c>
       <c r="E78">
-        <v>-19.37628265968953</v>
+        <v>-17.40854097252166</v>
       </c>
       <c r="F78">
-        <v>-1.935338104695271</v>
+        <v>-2.128522495069546</v>
       </c>
       <c r="G78">
-        <v>-0.8784223293075536</v>
+        <v>2.546600446051011</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.517337070956839</v>
       </c>
       <c r="E79">
-        <v>-18.41523786554685</v>
+        <v>-18.11233585720446</v>
       </c>
       <c r="F79">
-        <v>-2.218419410723557</v>
+        <v>-1.952156448074309</v>
       </c>
       <c r="G79">
-        <v>-0.1573894988784775</v>
+        <v>2.435403612426313</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.462065762876161</v>
       </c>
       <c r="E80">
-        <v>-19.81551798298075</v>
+        <v>-18.84854240306622</v>
       </c>
       <c r="F80">
-        <v>-1.821662902743901</v>
+        <v>-2.045399139668227</v>
       </c>
       <c r="G80">
-        <v>-0.819132319643371</v>
+        <v>2.230964035730005</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.396471187839675</v>
       </c>
       <c r="E81">
-        <v>-20.36900399660667</v>
+        <v>-19.39090611676425</v>
       </c>
       <c r="F81">
-        <v>-2.482309929131187</v>
+        <v>-2.131726620183575</v>
       </c>
       <c r="G81">
-        <v>0.1679458275985135</v>
+        <v>2.678576195876378</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.323289025202618</v>
       </c>
       <c r="E82">
-        <v>-21.22384702396216</v>
+        <v>-20.66193829776948</v>
       </c>
       <c r="F82">
-        <v>-2.421635330345735</v>
+        <v>-2.100501310935048</v>
       </c>
       <c r="G82">
-        <v>-0.2048711107570548</v>
+        <v>2.189706438956642</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.253461957186782</v>
       </c>
       <c r="E83">
-        <v>-22.9479987137175</v>
+        <v>-21.47276559150443</v>
       </c>
       <c r="F83">
-        <v>-2.432317956372237</v>
+        <v>-1.792417391588064</v>
       </c>
       <c r="G83">
-        <v>0.2201659409099614</v>
+        <v>2.843541314355053</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.195696292736009</v>
       </c>
       <c r="E84">
-        <v>-22.83010981026224</v>
+        <v>-21.88234698593637</v>
       </c>
       <c r="F84">
-        <v>-2.581065405790736</v>
+        <v>-1.881731964957907</v>
       </c>
       <c r="G84">
-        <v>-0.2347850222820309</v>
+        <v>3.091744802632193</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.154991073930892</v>
       </c>
       <c r="E85">
-        <v>-23.85753953422098</v>
+        <v>-23.37210388815237</v>
       </c>
       <c r="F85">
-        <v>-2.526425463534678</v>
+        <v>-2.088761688102573</v>
       </c>
       <c r="G85">
-        <v>0.7052005140253521</v>
+        <v>3.248245887146479</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.145521077232096</v>
       </c>
       <c r="E86">
-        <v>-24.24100138263107</v>
+        <v>-24.56451162556727</v>
       </c>
       <c r="F86">
-        <v>-2.426900433557929</v>
+        <v>-1.576582951319042</v>
       </c>
       <c r="G86">
-        <v>0.8519348030242833</v>
+        <v>3.415265661618361</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.168871597046421</v>
       </c>
       <c r="E87">
-        <v>-25.06052550088021</v>
+        <v>-25.33332918675158</v>
       </c>
       <c r="F87">
-        <v>-2.698867534142854</v>
+        <v>-1.713309961355517</v>
       </c>
       <c r="G87">
-        <v>0.6938202783526893</v>
+        <v>3.555350384143726</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.238507910886587</v>
       </c>
       <c r="E88">
-        <v>-26.29032459985255</v>
+        <v>-27.29747003970082</v>
       </c>
       <c r="F88">
-        <v>-2.410690940219948</v>
+        <v>-1.904745668142483</v>
       </c>
       <c r="G88">
-        <v>-0.1597470012442528</v>
+        <v>3.433786283747718</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.356561607167552</v>
       </c>
       <c r="E89">
-        <v>-28.49240085299555</v>
+        <v>-29.0299842204587</v>
       </c>
       <c r="F89">
-        <v>-2.364345440768121</v>
+        <v>-1.710286420335299</v>
       </c>
       <c r="G89">
-        <v>0.9493312407403555</v>
+        <v>4.22994590053067</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.527466076522848</v>
       </c>
       <c r="E90">
-        <v>-30.22490257411946</v>
+        <v>-30.28893678632567</v>
       </c>
       <c r="F90">
-        <v>-2.189317207128405</v>
+        <v>-1.687766424122791</v>
       </c>
       <c r="G90">
-        <v>1.09736306980107</v>
+        <v>3.440422796498328</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.7592602839398</v>
       </c>
       <c r="E91">
-        <v>-32.28566373532951</v>
+        <v>-32.12373210238011</v>
       </c>
       <c r="F91">
-        <v>-2.712864458147957</v>
+        <v>-1.730636093952471</v>
       </c>
       <c r="G91">
-        <v>2.049519897392223</v>
+        <v>3.644517754908609</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.047982045478303</v>
       </c>
       <c r="E92">
-        <v>-33.64016092772416</v>
+        <v>-33.24757032082209</v>
       </c>
       <c r="F92">
-        <v>-1.381797326755155</v>
+        <v>-1.144295280331106</v>
       </c>
       <c r="G92">
-        <v>0.6735191284121924</v>
+        <v>3.332557272971892</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.406340023572757</v>
       </c>
       <c r="E93">
-        <v>-35.31616236198511</v>
+        <v>-35.89046634737673</v>
       </c>
       <c r="F93">
-        <v>-1.857802915793237</v>
+        <v>-1.380524954424455</v>
       </c>
       <c r="G93">
-        <v>0.7491967818747932</v>
+        <v>3.529639771410443</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.826669428260754</v>
       </c>
       <c r="E94">
-        <v>-36.91155204103679</v>
+        <v>-37.43491481292374</v>
       </c>
       <c r="F94">
-        <v>-2.308768614979497</v>
+        <v>-1.510605972788269</v>
       </c>
       <c r="G94">
-        <v>0.5767101082291206</v>
+        <v>3.127248318326743</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.315033731101237</v>
       </c>
       <c r="E95">
-        <v>-40.13606793473175</v>
+        <v>-39.21420038301618</v>
       </c>
       <c r="F95">
-        <v>-2.738567870289423</v>
+        <v>-1.45598922481949</v>
       </c>
       <c r="G95">
-        <v>0.4837649900408965</v>
+        <v>3.037451758115401</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.872865626588507</v>
       </c>
       <c r="E96">
-        <v>-42.01323638932775</v>
+        <v>-41.16390882661164</v>
       </c>
       <c r="F96">
-        <v>-2.63827825719989</v>
+        <v>-1.746084317647279</v>
       </c>
       <c r="G96">
-        <v>-1.129377542383727</v>
+        <v>3.032282483824997</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.482807016517012</v>
       </c>
       <c r="E97">
-        <v>-42.88457804867112</v>
+        <v>-43.75317028211744</v>
       </c>
       <c r="F97">
-        <v>-2.333574076856328</v>
+        <v>-1.703219618022016</v>
       </c>
       <c r="G97">
-        <v>0.5760130394232934</v>
+        <v>2.829208326549841</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.156943674778628</v>
       </c>
       <c r="E98">
-        <v>-43.44672350790931</v>
+        <v>-45.65523100878881</v>
       </c>
       <c r="F98">
-        <v>-2.389533608385046</v>
+        <v>-1.257088270998495</v>
       </c>
       <c r="G98">
-        <v>0.2618960824543162</v>
+        <v>2.47418361258271</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.850749960916025</v>
       </c>
       <c r="E99">
-        <v>-48.03911097276769</v>
+        <v>-48.05804857810607</v>
       </c>
       <c r="F99">
-        <v>-2.720757142761831</v>
+        <v>-1.416402375007104</v>
       </c>
       <c r="G99">
-        <v>-1.342422133252344</v>
+        <v>2.822112322751195</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.590343718667516</v>
       </c>
       <c r="E100">
-        <v>-48.5542846502249</v>
+        <v>-49.9149753190077</v>
       </c>
       <c r="F100">
-        <v>-2.67328009343778</v>
+        <v>-1.667120194975416</v>
       </c>
       <c r="G100">
-        <v>-0.3481801028524453</v>
+        <v>2.548814357464274</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.29719530090609</v>
       </c>
       <c r="E101">
-        <v>-49.80806854459811</v>
+        <v>-51.96008925655146</v>
       </c>
       <c r="F101">
-        <v>-2.238558679020419</v>
+        <v>-1.661857576865431</v>
       </c>
       <c r="G101">
-        <v>-1.665316413536645</v>
+        <v>2.086574195373894</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.04101329214414</v>
       </c>
       <c r="E102">
-        <v>-51.95328110488723</v>
+        <v>-54.27151541066587</v>
       </c>
       <c r="F102">
-        <v>-3.055057233672613</v>
+        <v>-1.972950126619383</v>
       </c>
       <c r="G102">
-        <v>-0.2327695274576914</v>
+        <v>1.634782233137149</v>
       </c>
     </row>
   </sheetData>
